--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,9 @@
     <t>['5', '63']</t>
   </si>
   <si>
+    <t>['58']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -908,6 +911,9 @@
   </si>
   <si>
     <t>['85', '90+6']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP184"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1531,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1812,7 +1818,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1937,7 +1943,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2143,7 +2149,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2349,7 +2355,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2555,7 +2561,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2761,7 +2767,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2967,7 +2973,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3251,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
         <v>0.11</v>
@@ -3379,7 +3385,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3791,7 +3797,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -5027,7 +5033,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q19">
         <v>3.2</v>
@@ -5311,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5520,7 +5526,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5645,7 +5651,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6057,7 +6063,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6547,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26">
         <v>0.89</v>
@@ -6881,7 +6887,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8117,7 +8123,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8607,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36">
         <v>1.11</v>
@@ -8735,7 +8741,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8941,7 +8947,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9022,7 +9028,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR38">
         <v>1.9</v>
@@ -9434,7 +9440,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR40">
         <v>2.11</v>
@@ -9765,7 +9771,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9971,7 +9977,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10383,7 +10389,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10795,7 +10801,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11001,7 +11007,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11825,7 +11831,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q52">
         <v>2.88</v>
@@ -12031,7 +12037,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12315,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>0.67</v>
@@ -12521,7 +12527,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ55">
         <v>1.56</v>
@@ -12649,7 +12655,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12936,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR57">
         <v>1.38</v>
@@ -13061,7 +13067,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13679,7 +13685,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14091,7 +14097,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14503,7 +14509,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14709,7 +14715,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15327,7 +15333,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15533,7 +15539,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15614,7 +15620,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR70">
         <v>1.36</v>
@@ -15945,7 +15951,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16023,7 +16029,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
         <v>1.67</v>
@@ -16769,7 +16775,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17056,7 +17062,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR77">
         <v>1.31</v>
@@ -17181,7 +17187,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17593,7 +17599,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17799,7 +17805,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18829,7 +18835,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -18907,7 +18913,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
         <v>1.3</v>
@@ -19241,7 +19247,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19447,7 +19453,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19525,7 +19531,7 @@
         <v>2.4</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ89">
         <v>2.09</v>
@@ -19734,7 +19740,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR90">
         <v>1.55</v>
@@ -19859,7 +19865,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20065,7 +20071,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20143,7 +20149,7 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92">
         <v>0.33</v>
@@ -20477,7 +20483,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20558,7 +20564,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20889,7 +20895,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21301,7 +21307,7 @@
         <v>163</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98">
         <v>1.83</v>
@@ -21919,7 +21925,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22125,7 +22131,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22331,7 +22337,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22409,7 +22415,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
         <v>1.89</v>
@@ -22824,7 +22830,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -22949,7 +22955,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23773,7 +23779,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24263,7 +24269,7 @@
         <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112">
         <v>1.67</v>
@@ -24597,7 +24603,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25009,7 +25015,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25215,7 +25221,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25421,7 +25427,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25502,7 +25508,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25833,7 +25839,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26657,7 +26663,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27150,7 +27156,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27353,7 +27359,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27893,7 +27899,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -27974,7 +27980,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR130">
         <v>1.31</v>
@@ -28305,7 +28311,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28717,7 +28723,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28923,7 +28929,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29335,7 +29341,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29747,7 +29753,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29953,7 +29959,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30237,7 +30243,7 @@
         <v>0.57</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ141">
         <v>0.89</v>
@@ -30571,7 +30577,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30649,7 +30655,7 @@
         <v>1.71</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ143">
         <v>2</v>
@@ -30777,7 +30783,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30858,7 +30864,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR144">
         <v>1.51</v>
@@ -31189,7 +31195,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31476,7 +31482,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -31807,7 +31813,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32013,7 +32019,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32631,7 +32637,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33043,7 +33049,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33249,7 +33255,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33661,7 +33667,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33867,7 +33873,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34357,7 +34363,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ161">
         <v>0.33</v>
@@ -34772,7 +34778,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR163">
         <v>1.23</v>
@@ -35103,7 +35109,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35515,7 +35521,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35593,7 +35599,7 @@
         <v>1.57</v>
       </c>
       <c r="AP167">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ167">
         <v>1.67</v>
@@ -35927,7 +35933,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36008,7 +36014,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ169">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36339,7 +36345,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37369,7 +37375,7 @@
         <v>214</v>
       </c>
       <c r="P176" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37575,7 +37581,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37781,7 +37787,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37987,7 +37993,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38193,7 +38199,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38811,7 +38817,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39174,6 +39180,418 @@
       </c>
       <c r="BP184">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7465178</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F185">
+        <v>19</v>
+      </c>
+      <c r="G185" t="s">
+        <v>86</v>
+      </c>
+      <c r="H185" t="s">
+        <v>89</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
+        <v>104</v>
+      </c>
+      <c r="P185" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q185">
+        <v>3.25</v>
+      </c>
+      <c r="R185">
+        <v>2.1</v>
+      </c>
+      <c r="S185">
+        <v>3.4</v>
+      </c>
+      <c r="T185">
+        <v>1.4</v>
+      </c>
+      <c r="U185">
+        <v>2.75</v>
+      </c>
+      <c r="V185">
+        <v>3</v>
+      </c>
+      <c r="W185">
+        <v>1.36</v>
+      </c>
+      <c r="X185">
+        <v>9</v>
+      </c>
+      <c r="Y185">
+        <v>1.07</v>
+      </c>
+      <c r="Z185">
+        <v>2.63</v>
+      </c>
+      <c r="AA185">
+        <v>3.2</v>
+      </c>
+      <c r="AB185">
+        <v>2.75</v>
+      </c>
+      <c r="AC185">
+        <v>1.08</v>
+      </c>
+      <c r="AD185">
+        <v>8.5</v>
+      </c>
+      <c r="AE185">
+        <v>1.4</v>
+      </c>
+      <c r="AF185">
+        <v>3</v>
+      </c>
+      <c r="AG185">
+        <v>2</v>
+      </c>
+      <c r="AH185">
+        <v>1.8</v>
+      </c>
+      <c r="AI185">
+        <v>1.75</v>
+      </c>
+      <c r="AJ185">
+        <v>2</v>
+      </c>
+      <c r="AK185">
+        <v>1.47</v>
+      </c>
+      <c r="AL185">
+        <v>1.35</v>
+      </c>
+      <c r="AM185">
+        <v>1.42</v>
+      </c>
+      <c r="AN185">
+        <v>1.5</v>
+      </c>
+      <c r="AO185">
+        <v>1</v>
+      </c>
+      <c r="AP185">
+        <v>1.33</v>
+      </c>
+      <c r="AQ185">
+        <v>1.2</v>
+      </c>
+      <c r="AR185">
+        <v>1.15</v>
+      </c>
+      <c r="AS185">
+        <v>1.13</v>
+      </c>
+      <c r="AT185">
+        <v>2.28</v>
+      </c>
+      <c r="AU185">
+        <v>3</v>
+      </c>
+      <c r="AV185">
+        <v>2</v>
+      </c>
+      <c r="AW185">
+        <v>9</v>
+      </c>
+      <c r="AX185">
+        <v>2</v>
+      </c>
+      <c r="AY185">
+        <v>15</v>
+      </c>
+      <c r="AZ185">
+        <v>5</v>
+      </c>
+      <c r="BA185">
+        <v>6</v>
+      </c>
+      <c r="BB185">
+        <v>3</v>
+      </c>
+      <c r="BC185">
+        <v>9</v>
+      </c>
+      <c r="BD185">
+        <v>1.89</v>
+      </c>
+      <c r="BE185">
+        <v>6.4</v>
+      </c>
+      <c r="BF185">
+        <v>2.12</v>
+      </c>
+      <c r="BG185">
+        <v>1.41</v>
+      </c>
+      <c r="BH185">
+        <v>2.65</v>
+      </c>
+      <c r="BI185">
+        <v>1.68</v>
+      </c>
+      <c r="BJ185">
+        <v>2.02</v>
+      </c>
+      <c r="BK185">
+        <v>2.08</v>
+      </c>
+      <c r="BL185">
+        <v>1.65</v>
+      </c>
+      <c r="BM185">
+        <v>2.7</v>
+      </c>
+      <c r="BN185">
+        <v>1.4</v>
+      </c>
+      <c r="BO185">
+        <v>3.55</v>
+      </c>
+      <c r="BP185">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7465180</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45668.51041666666</v>
+      </c>
+      <c r="F186">
+        <v>19</v>
+      </c>
+      <c r="G186" t="s">
+        <v>78</v>
+      </c>
+      <c r="H186" t="s">
+        <v>71</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
+        <v>221</v>
+      </c>
+      <c r="P186" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q186">
+        <v>4.5</v>
+      </c>
+      <c r="R186">
+        <v>2.2</v>
+      </c>
+      <c r="S186">
+        <v>2.5</v>
+      </c>
+      <c r="T186">
+        <v>1.4</v>
+      </c>
+      <c r="U186">
+        <v>2.75</v>
+      </c>
+      <c r="V186">
+        <v>3</v>
+      </c>
+      <c r="W186">
+        <v>1.36</v>
+      </c>
+      <c r="X186">
+        <v>8</v>
+      </c>
+      <c r="Y186">
+        <v>1.08</v>
+      </c>
+      <c r="Z186">
+        <v>4</v>
+      </c>
+      <c r="AA186">
+        <v>3.6</v>
+      </c>
+      <c r="AB186">
+        <v>1.85</v>
+      </c>
+      <c r="AC186">
+        <v>1.07</v>
+      </c>
+      <c r="AD186">
+        <v>10</v>
+      </c>
+      <c r="AE186">
+        <v>1.36</v>
+      </c>
+      <c r="AF186">
+        <v>3.2</v>
+      </c>
+      <c r="AG186">
+        <v>2</v>
+      </c>
+      <c r="AH186">
+        <v>1.8</v>
+      </c>
+      <c r="AI186">
+        <v>1.8</v>
+      </c>
+      <c r="AJ186">
+        <v>1.95</v>
+      </c>
+      <c r="AK186">
+        <v>1.9</v>
+      </c>
+      <c r="AL186">
+        <v>1.3</v>
+      </c>
+      <c r="AM186">
+        <v>1.21</v>
+      </c>
+      <c r="AN186">
+        <v>1</v>
+      </c>
+      <c r="AO186">
+        <v>1</v>
+      </c>
+      <c r="AP186">
+        <v>1.2</v>
+      </c>
+      <c r="AQ186">
+        <v>0.9</v>
+      </c>
+      <c r="AR186">
+        <v>1.03</v>
+      </c>
+      <c r="AS186">
+        <v>1.2</v>
+      </c>
+      <c r="AT186">
+        <v>2.23</v>
+      </c>
+      <c r="AU186">
+        <v>2</v>
+      </c>
+      <c r="AV186">
+        <v>4</v>
+      </c>
+      <c r="AW186">
+        <v>11</v>
+      </c>
+      <c r="AX186">
+        <v>11</v>
+      </c>
+      <c r="AY186">
+        <v>18</v>
+      </c>
+      <c r="AZ186">
+        <v>18</v>
+      </c>
+      <c r="BA186">
+        <v>1</v>
+      </c>
+      <c r="BB186">
+        <v>8</v>
+      </c>
+      <c r="BC186">
+        <v>9</v>
+      </c>
+      <c r="BD186">
+        <v>2.65</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>1.56</v>
+      </c>
+      <c r="BG186">
+        <v>1.32</v>
+      </c>
+      <c r="BH186">
+        <v>3.05</v>
+      </c>
+      <c r="BI186">
+        <v>1.55</v>
+      </c>
+      <c r="BJ186">
+        <v>2.25</v>
+      </c>
+      <c r="BK186">
+        <v>1.9</v>
+      </c>
+      <c r="BL186">
+        <v>1.79</v>
+      </c>
+      <c r="BM186">
+        <v>2.4</v>
+      </c>
+      <c r="BN186">
+        <v>1.5</v>
+      </c>
+      <c r="BO186">
+        <v>3.05</v>
+      </c>
+      <c r="BP186">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="301">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,12 @@
     <t>['58']</t>
   </si>
   <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -707,9 +713,6 @@
   </si>
   <si>
     <t>['2', '90+5']</t>
-  </si>
-  <si>
-    <t>['90+3']</t>
   </si>
   <si>
     <t>['12', '31', '80']</t>
@@ -1275,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1534,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1943,7 +1946,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2149,7 +2152,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2355,7 +2358,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2436,7 +2439,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ6">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2561,7 +2564,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2767,7 +2770,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2973,7 +2976,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3385,7 +3388,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3672,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -3797,7 +3800,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3875,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ13">
         <v>1.89</v>
@@ -4493,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>1.56</v>
@@ -5033,7 +5036,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Q19">
         <v>3.2</v>
@@ -5651,7 +5654,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6063,7 +6066,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6350,7 +6353,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ25">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR25">
         <v>0.96</v>
@@ -6556,7 +6559,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ26">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6887,7 +6890,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7995,7 +7998,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
         <v>1.3</v>
@@ -8123,7 +8126,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8741,7 +8744,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8947,7 +8950,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9025,7 +9028,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ38">
         <v>1.2</v>
@@ -9646,7 +9649,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ41">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR41">
         <v>1.59</v>
@@ -9771,7 +9774,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9977,7 +9980,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10055,7 +10058,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
         <v>0.5</v>
@@ -10261,7 +10264,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ44">
         <v>0.25</v>
@@ -10389,7 +10392,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10801,7 +10804,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11007,7 +11010,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11294,7 +11297,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR49">
         <v>1.74</v>
@@ -11831,7 +11834,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Q52">
         <v>2.88</v>
@@ -12037,7 +12040,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12655,7 +12658,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13067,7 +13070,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13354,7 +13357,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ59">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR59">
         <v>1.14</v>
@@ -13685,7 +13688,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14097,7 +14100,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14509,7 +14512,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14587,7 +14590,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ65">
         <v>0.33</v>
@@ -14715,7 +14718,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15333,7 +15336,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15411,7 +15414,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>1.89</v>
@@ -15539,7 +15542,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15951,7 +15954,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16444,7 +16447,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR74">
         <v>1.48</v>
@@ -16650,7 +16653,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ75">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR75">
         <v>1.11</v>
@@ -16775,7 +16778,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17187,7 +17190,7 @@
         <v>128</v>
       </c>
       <c r="P78" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17599,7 +17602,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17805,7 +17808,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18092,7 +18095,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ82">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR82">
         <v>1.25</v>
@@ -18295,7 +18298,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83">
         <v>1.67</v>
@@ -18835,7 +18838,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19247,7 +19250,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19453,7 +19456,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19737,7 +19740,7 @@
         <v>0.67</v>
       </c>
       <c r="AP90">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ90">
         <v>0.9</v>
@@ -19865,7 +19868,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20071,7 +20074,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20483,7 +20486,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20895,7 +20898,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21307,7 +21310,7 @@
         <v>163</v>
       </c>
       <c r="P98" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q98">
         <v>1.83</v>
@@ -21388,7 +21391,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ98">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR98">
         <v>1.58</v>
@@ -21925,7 +21928,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22131,7 +22134,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22209,7 +22212,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>0.67</v>
@@ -22337,7 +22340,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22955,7 +22958,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23448,7 +23451,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ108">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -23779,7 +23782,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24603,7 +24606,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24684,7 +24687,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ114">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR114">
         <v>1.33</v>
@@ -25015,7 +25018,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25221,7 +25224,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25299,7 +25302,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ117">
         <v>1.56</v>
@@ -25427,7 +25430,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25839,7 +25842,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26663,7 +26666,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27899,7 +27902,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28311,7 +28314,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28723,7 +28726,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28929,7 +28932,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29213,7 +29216,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ136">
         <v>1.3</v>
@@ -29341,7 +29344,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29753,7 +29756,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29834,7 +29837,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR139">
         <v>1.33</v>
@@ -29959,7 +29962,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30246,7 +30249,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ141">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR141">
         <v>1.08</v>
@@ -30449,7 +30452,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142">
         <v>0.44</v>
@@ -30577,7 +30580,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30783,7 +30786,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31195,7 +31198,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31685,7 +31688,7 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ148">
         <v>0.88</v>
@@ -31813,7 +31816,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32019,7 +32022,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32637,7 +32640,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33049,7 +33052,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33255,7 +33258,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33667,7 +33670,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33873,7 +33876,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34366,7 +34369,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ161">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR161">
         <v>1.1</v>
@@ -34569,7 +34572,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ162">
         <v>0.88</v>
@@ -34981,7 +34984,7 @@
         <v>0.57</v>
       </c>
       <c r="AP164">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ164">
         <v>0.44</v>
@@ -35109,7 +35112,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35521,7 +35524,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35933,7 +35936,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36220,7 +36223,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ170">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR170">
         <v>1.98</v>
@@ -36345,7 +36348,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36423,10 +36426,10 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ171">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR171">
         <v>1.12</v>
@@ -37375,7 +37378,7 @@
         <v>214</v>
       </c>
       <c r="P176" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37581,7 +37584,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37787,7 +37790,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37993,7 +37996,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38199,7 +38202,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38817,7 +38820,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39229,7 +39232,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39592,6 +39595,418 @@
       </c>
       <c r="BP186">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7469584</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45668.60416666666</v>
+      </c>
+      <c r="F187">
+        <v>19</v>
+      </c>
+      <c r="G187" t="s">
+        <v>82</v>
+      </c>
+      <c r="H187" t="s">
+        <v>85</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>1</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>222</v>
+      </c>
+      <c r="P187" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q187">
+        <v>2.88</v>
+      </c>
+      <c r="R187">
+        <v>1.95</v>
+      </c>
+      <c r="S187">
+        <v>4.5</v>
+      </c>
+      <c r="T187">
+        <v>1.57</v>
+      </c>
+      <c r="U187">
+        <v>2.25</v>
+      </c>
+      <c r="V187">
+        <v>3.75</v>
+      </c>
+      <c r="W187">
+        <v>1.25</v>
+      </c>
+      <c r="X187">
+        <v>11</v>
+      </c>
+      <c r="Y187">
+        <v>1.05</v>
+      </c>
+      <c r="Z187">
+        <v>2.05</v>
+      </c>
+      <c r="AA187">
+        <v>3.2</v>
+      </c>
+      <c r="AB187">
+        <v>3.8</v>
+      </c>
+      <c r="AC187">
+        <v>1.12</v>
+      </c>
+      <c r="AD187">
+        <v>6.5</v>
+      </c>
+      <c r="AE187">
+        <v>1.55</v>
+      </c>
+      <c r="AF187">
+        <v>2.3</v>
+      </c>
+      <c r="AG187">
+        <v>2.5</v>
+      </c>
+      <c r="AH187">
+        <v>1.53</v>
+      </c>
+      <c r="AI187">
+        <v>2.1</v>
+      </c>
+      <c r="AJ187">
+        <v>1.67</v>
+      </c>
+      <c r="AK187">
+        <v>1.22</v>
+      </c>
+      <c r="AL187">
+        <v>1.38</v>
+      </c>
+      <c r="AM187">
+        <v>1.73</v>
+      </c>
+      <c r="AN187">
+        <v>1.56</v>
+      </c>
+      <c r="AO187">
+        <v>0.89</v>
+      </c>
+      <c r="AP187">
+        <v>1.5</v>
+      </c>
+      <c r="AQ187">
+        <v>0.9</v>
+      </c>
+      <c r="AR187">
+        <v>1.12</v>
+      </c>
+      <c r="AS187">
+        <v>0.82</v>
+      </c>
+      <c r="AT187">
+        <v>1.94</v>
+      </c>
+      <c r="AU187">
+        <v>6</v>
+      </c>
+      <c r="AV187">
+        <v>7</v>
+      </c>
+      <c r="AW187">
+        <v>10</v>
+      </c>
+      <c r="AX187">
+        <v>8</v>
+      </c>
+      <c r="AY187">
+        <v>18</v>
+      </c>
+      <c r="AZ187">
+        <v>16</v>
+      </c>
+      <c r="BA187">
+        <v>8</v>
+      </c>
+      <c r="BB187">
+        <v>4</v>
+      </c>
+      <c r="BC187">
+        <v>12</v>
+      </c>
+      <c r="BD187">
+        <v>1.58</v>
+      </c>
+      <c r="BE187">
+        <v>6.4</v>
+      </c>
+      <c r="BF187">
+        <v>2.65</v>
+      </c>
+      <c r="BG187">
+        <v>1.5</v>
+      </c>
+      <c r="BH187">
+        <v>2.33</v>
+      </c>
+      <c r="BI187">
+        <v>1.86</v>
+      </c>
+      <c r="BJ187">
+        <v>1.82</v>
+      </c>
+      <c r="BK187">
+        <v>2.38</v>
+      </c>
+      <c r="BL187">
+        <v>1.5</v>
+      </c>
+      <c r="BM187">
+        <v>3.15</v>
+      </c>
+      <c r="BN187">
+        <v>1.3</v>
+      </c>
+      <c r="BO187">
+        <v>4.3</v>
+      </c>
+      <c r="BP187">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7465177</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45668.70833333334</v>
+      </c>
+      <c r="F188">
+        <v>19</v>
+      </c>
+      <c r="G188" t="s">
+        <v>80</v>
+      </c>
+      <c r="H188" t="s">
+        <v>75</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>223</v>
+      </c>
+      <c r="P188" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q188">
+        <v>2.88</v>
+      </c>
+      <c r="R188">
+        <v>1.91</v>
+      </c>
+      <c r="S188">
+        <v>4.5</v>
+      </c>
+      <c r="T188">
+        <v>1.57</v>
+      </c>
+      <c r="U188">
+        <v>2.25</v>
+      </c>
+      <c r="V188">
+        <v>3.75</v>
+      </c>
+      <c r="W188">
+        <v>1.25</v>
+      </c>
+      <c r="X188">
+        <v>13</v>
+      </c>
+      <c r="Y188">
+        <v>1.04</v>
+      </c>
+      <c r="Z188">
+        <v>2.1</v>
+      </c>
+      <c r="AA188">
+        <v>3.1</v>
+      </c>
+      <c r="AB188">
+        <v>3.7</v>
+      </c>
+      <c r="AC188">
+        <v>1.07</v>
+      </c>
+      <c r="AD188">
+        <v>9</v>
+      </c>
+      <c r="AE188">
+        <v>1.5</v>
+      </c>
+      <c r="AF188">
+        <v>2.45</v>
+      </c>
+      <c r="AG188">
+        <v>2.5</v>
+      </c>
+      <c r="AH188">
+        <v>1.53</v>
+      </c>
+      <c r="AI188">
+        <v>2.1</v>
+      </c>
+      <c r="AJ188">
+        <v>1.67</v>
+      </c>
+      <c r="AK188">
+        <v>1.24</v>
+      </c>
+      <c r="AL188">
+        <v>1.32</v>
+      </c>
+      <c r="AM188">
+        <v>1.78</v>
+      </c>
+      <c r="AN188">
+        <v>1.78</v>
+      </c>
+      <c r="AO188">
+        <v>0.33</v>
+      </c>
+      <c r="AP188">
+        <v>1.7</v>
+      </c>
+      <c r="AQ188">
+        <v>0.4</v>
+      </c>
+      <c r="AR188">
+        <v>1.34</v>
+      </c>
+      <c r="AS188">
+        <v>0.95</v>
+      </c>
+      <c r="AT188">
+        <v>2.29</v>
+      </c>
+      <c r="AU188">
+        <v>6</v>
+      </c>
+      <c r="AV188">
+        <v>2</v>
+      </c>
+      <c r="AW188">
+        <v>10</v>
+      </c>
+      <c r="AX188">
+        <v>4</v>
+      </c>
+      <c r="AY188">
+        <v>19</v>
+      </c>
+      <c r="AZ188">
+        <v>7</v>
+      </c>
+      <c r="BA188">
+        <v>10</v>
+      </c>
+      <c r="BB188">
+        <v>1</v>
+      </c>
+      <c r="BC188">
+        <v>11</v>
+      </c>
+      <c r="BD188">
+        <v>1.57</v>
+      </c>
+      <c r="BE188">
+        <v>6.4</v>
+      </c>
+      <c r="BF188">
+        <v>2.65</v>
+      </c>
+      <c r="BG188">
+        <v>1.37</v>
+      </c>
+      <c r="BH188">
+        <v>2.8</v>
+      </c>
+      <c r="BI188">
+        <v>1.64</v>
+      </c>
+      <c r="BJ188">
+        <v>2.1</v>
+      </c>
+      <c r="BK188">
+        <v>2.02</v>
+      </c>
+      <c r="BL188">
+        <v>1.68</v>
+      </c>
+      <c r="BM188">
+        <v>2.55</v>
+      </c>
+      <c r="BN188">
+        <v>1.43</v>
+      </c>
+      <c r="BO188">
+        <v>3.4</v>
+      </c>
+      <c r="BP188">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,9 @@
     <t>['90+3']</t>
   </si>
   <si>
+    <t>['88']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -917,6 +920,9 @@
   </si>
   <si>
     <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['70', '86']</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1534,7 +1540,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1615,7 +1621,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1946,7 +1952,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2152,7 +2158,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2230,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
         <v>0.67</v>
@@ -2358,7 +2364,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2564,7 +2570,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2770,7 +2776,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2976,7 +2982,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3388,7 +3394,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3800,7 +3806,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -5526,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ21">
         <v>1.2</v>
@@ -5654,7 +5660,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6066,7 +6072,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6762,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ27">
         <v>0.11</v>
@@ -6890,7 +6896,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7177,7 +7183,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ29">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7380,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
         <v>1.9</v>
@@ -8126,7 +8132,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8744,7 +8750,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8950,7 +8956,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9774,7 +9780,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9980,7 +9986,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10267,7 +10273,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ44">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10392,7 +10398,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10804,7 +10810,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11010,7 +11016,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11088,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
         <v>1.67</v>
@@ -11294,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ49">
         <v>0.4</v>
@@ -11503,7 +11509,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ50">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -11915,7 +11921,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ52">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12040,7 +12046,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12658,7 +12664,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13070,7 +13076,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13688,7 +13694,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14100,7 +14106,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14387,7 +14393,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -14512,7 +14518,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14718,7 +14724,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15211,7 +15217,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ68">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -15336,7 +15342,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15542,7 +15548,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15620,7 +15626,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
         <v>0.9</v>
@@ -15954,7 +15960,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16778,7 +16784,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17602,7 +17608,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17680,7 +17686,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ80">
         <v>1.9</v>
@@ -17808,7 +17814,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18507,7 +18513,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -18710,7 +18716,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85">
         <v>0.44</v>
@@ -18838,7 +18844,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19250,7 +19256,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19456,7 +19462,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19868,7 +19874,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20074,7 +20080,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20486,7 +20492,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20898,7 +20904,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21310,7 +21316,7 @@
         <v>163</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q98">
         <v>1.83</v>
@@ -21388,7 +21394,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ98">
         <v>0.9</v>
@@ -21597,7 +21603,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ99">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -21928,7 +21934,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22134,7 +22140,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22340,7 +22346,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22830,7 +22836,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ105">
         <v>1.2</v>
@@ -22958,7 +22964,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23782,7 +23788,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23863,7 +23869,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ110">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -24606,7 +24612,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24890,7 +24896,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ115">
         <v>1.11</v>
@@ -25018,7 +25024,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25224,7 +25230,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25430,7 +25436,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25717,7 +25723,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25842,7 +25848,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26129,7 +26135,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ121">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -26666,7 +26672,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27902,7 +27908,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28186,7 +28192,7 @@
         <v>0.43</v>
       </c>
       <c r="AP131">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ131">
         <v>0.5</v>
@@ -28314,7 +28320,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28392,7 +28398,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ132">
         <v>1.67</v>
@@ -28726,7 +28732,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28932,7 +28938,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29344,7 +29350,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29756,7 +29762,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29962,7 +29968,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30580,7 +30586,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30786,7 +30792,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31073,7 +31079,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ145">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -31198,7 +31204,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31691,7 +31697,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ148">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -31816,7 +31822,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32022,7 +32028,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32512,7 +32518,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ152">
         <v>0.33</v>
@@ -32640,7 +32646,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33052,7 +33058,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33258,7 +33264,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33670,7 +33676,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33876,7 +33882,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -33954,7 +33960,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ159">
         <v>0.67</v>
@@ -34575,7 +34581,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ162">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -35112,7 +35118,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35396,10 +35402,10 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ166">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -35524,7 +35530,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35936,7 +35942,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36348,7 +36354,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37378,7 +37384,7 @@
         <v>214</v>
       </c>
       <c r="P176" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37584,7 +37590,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37790,7 +37796,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37996,7 +38002,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38202,7 +38208,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38486,7 +38492,7 @@
         <v>0.13</v>
       </c>
       <c r="AP181">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ181">
         <v>0.11</v>
@@ -38820,7 +38826,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39128,13 +39134,13 @@
         <v>3</v>
       </c>
       <c r="AX184">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AY184">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ184">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BA184">
         <v>3</v>
@@ -39232,7 +39238,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39331,16 +39337,16 @@
         <v>2</v>
       </c>
       <c r="AW185">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX185">
         <v>2</v>
       </c>
       <c r="AY185">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ185">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA185">
         <v>6</v>
@@ -39537,16 +39543,16 @@
         <v>4</v>
       </c>
       <c r="AW186">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX186">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY186">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ186">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA186">
         <v>1</v>
@@ -39743,16 +39749,16 @@
         <v>7</v>
       </c>
       <c r="AW187">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX187">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY187">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ187">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA187">
         <v>8</v>
@@ -39949,16 +39955,16 @@
         <v>2</v>
       </c>
       <c r="AW188">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY188">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ188">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA188">
         <v>10</v>
@@ -40007,6 +40013,418 @@
       </c>
       <c r="BP188">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7465182</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45669.41666666666</v>
+      </c>
+      <c r="F189">
+        <v>19</v>
+      </c>
+      <c r="G189" t="s">
+        <v>73</v>
+      </c>
+      <c r="H189" t="s">
+        <v>83</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>2</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+      <c r="O189" t="s">
+        <v>224</v>
+      </c>
+      <c r="P189" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q189">
+        <v>3.2</v>
+      </c>
+      <c r="R189">
+        <v>1.95</v>
+      </c>
+      <c r="S189">
+        <v>4</v>
+      </c>
+      <c r="T189">
+        <v>1.53</v>
+      </c>
+      <c r="U189">
+        <v>2.38</v>
+      </c>
+      <c r="V189">
+        <v>3.75</v>
+      </c>
+      <c r="W189">
+        <v>1.25</v>
+      </c>
+      <c r="X189">
+        <v>11</v>
+      </c>
+      <c r="Y189">
+        <v>1.05</v>
+      </c>
+      <c r="Z189">
+        <v>2.38</v>
+      </c>
+      <c r="AA189">
+        <v>3</v>
+      </c>
+      <c r="AB189">
+        <v>3.2</v>
+      </c>
+      <c r="AC189">
+        <v>1.12</v>
+      </c>
+      <c r="AD189">
+        <v>6.5</v>
+      </c>
+      <c r="AE189">
+        <v>1.52</v>
+      </c>
+      <c r="AF189">
+        <v>2.37</v>
+      </c>
+      <c r="AG189">
+        <v>2.5</v>
+      </c>
+      <c r="AH189">
+        <v>1.53</v>
+      </c>
+      <c r="AI189">
+        <v>2</v>
+      </c>
+      <c r="AJ189">
+        <v>1.75</v>
+      </c>
+      <c r="AK189">
+        <v>1.35</v>
+      </c>
+      <c r="AL189">
+        <v>1.38</v>
+      </c>
+      <c r="AM189">
+        <v>1.52</v>
+      </c>
+      <c r="AN189">
+        <v>1.33</v>
+      </c>
+      <c r="AO189">
+        <v>0.25</v>
+      </c>
+      <c r="AP189">
+        <v>1.2</v>
+      </c>
+      <c r="AQ189">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR189">
+        <v>1.34</v>
+      </c>
+      <c r="AS189">
+        <v>1.06</v>
+      </c>
+      <c r="AT189">
+        <v>2.4</v>
+      </c>
+      <c r="AU189">
+        <v>8</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>4</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>16</v>
+      </c>
+      <c r="AZ189">
+        <v>13</v>
+      </c>
+      <c r="BA189">
+        <v>4</v>
+      </c>
+      <c r="BB189">
+        <v>5</v>
+      </c>
+      <c r="BC189">
+        <v>9</v>
+      </c>
+      <c r="BD189">
+        <v>1.76</v>
+      </c>
+      <c r="BE189">
+        <v>6.25</v>
+      </c>
+      <c r="BF189">
+        <v>2.3</v>
+      </c>
+      <c r="BG189">
+        <v>1.48</v>
+      </c>
+      <c r="BH189">
+        <v>2.45</v>
+      </c>
+      <c r="BI189">
+        <v>1.79</v>
+      </c>
+      <c r="BJ189">
+        <v>1.9</v>
+      </c>
+      <c r="BK189">
+        <v>2.25</v>
+      </c>
+      <c r="BL189">
+        <v>1.55</v>
+      </c>
+      <c r="BM189">
+        <v>2.9</v>
+      </c>
+      <c r="BN189">
+        <v>1.34</v>
+      </c>
+      <c r="BO189">
+        <v>3.9</v>
+      </c>
+      <c r="BP189">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7465175</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45669.51041666666</v>
+      </c>
+      <c r="F190">
+        <v>19</v>
+      </c>
+      <c r="G190" t="s">
+        <v>87</v>
+      </c>
+      <c r="H190" t="s">
+        <v>74</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
+        <v>102</v>
+      </c>
+      <c r="P190" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q190">
+        <v>1.91</v>
+      </c>
+      <c r="R190">
+        <v>2.25</v>
+      </c>
+      <c r="S190">
+        <v>8.5</v>
+      </c>
+      <c r="T190">
+        <v>1.4</v>
+      </c>
+      <c r="U190">
+        <v>2.75</v>
+      </c>
+      <c r="V190">
+        <v>3</v>
+      </c>
+      <c r="W190">
+        <v>1.36</v>
+      </c>
+      <c r="X190">
+        <v>9</v>
+      </c>
+      <c r="Y190">
+        <v>1.07</v>
+      </c>
+      <c r="Z190">
+        <v>1.38</v>
+      </c>
+      <c r="AA190">
+        <v>4.75</v>
+      </c>
+      <c r="AB190">
+        <v>8</v>
+      </c>
+      <c r="AC190">
+        <v>1.03</v>
+      </c>
+      <c r="AD190">
+        <v>13</v>
+      </c>
+      <c r="AE190">
+        <v>1.25</v>
+      </c>
+      <c r="AF190">
+        <v>4</v>
+      </c>
+      <c r="AG190">
+        <v>2</v>
+      </c>
+      <c r="AH190">
+        <v>1.8</v>
+      </c>
+      <c r="AI190">
+        <v>2.38</v>
+      </c>
+      <c r="AJ190">
+        <v>1.53</v>
+      </c>
+      <c r="AK190">
+        <v>1.06</v>
+      </c>
+      <c r="AL190">
+        <v>1.17</v>
+      </c>
+      <c r="AM190">
+        <v>3.25</v>
+      </c>
+      <c r="AN190">
+        <v>2.56</v>
+      </c>
+      <c r="AO190">
+        <v>0.88</v>
+      </c>
+      <c r="AP190">
+        <v>2.6</v>
+      </c>
+      <c r="AQ190">
+        <v>0.78</v>
+      </c>
+      <c r="AR190">
+        <v>1.72</v>
+      </c>
+      <c r="AS190">
+        <v>0.74</v>
+      </c>
+      <c r="AT190">
+        <v>2.46</v>
+      </c>
+      <c r="AU190">
+        <v>6</v>
+      </c>
+      <c r="AV190">
+        <v>2</v>
+      </c>
+      <c r="AW190">
+        <v>3</v>
+      </c>
+      <c r="AX190">
+        <v>4</v>
+      </c>
+      <c r="AY190">
+        <v>10</v>
+      </c>
+      <c r="AZ190">
+        <v>7</v>
+      </c>
+      <c r="BA190">
+        <v>4</v>
+      </c>
+      <c r="BB190">
+        <v>0</v>
+      </c>
+      <c r="BC190">
+        <v>4</v>
+      </c>
+      <c r="BD190">
+        <v>1.3</v>
+      </c>
+      <c r="BE190">
+        <v>7.5</v>
+      </c>
+      <c r="BF190">
+        <v>3.9</v>
+      </c>
+      <c r="BG190">
+        <v>1.3</v>
+      </c>
+      <c r="BH190">
+        <v>3.05</v>
+      </c>
+      <c r="BI190">
+        <v>1.54</v>
+      </c>
+      <c r="BJ190">
+        <v>2.3</v>
+      </c>
+      <c r="BK190">
+        <v>1.9</v>
+      </c>
+      <c r="BL190">
+        <v>1.79</v>
+      </c>
+      <c r="BM190">
+        <v>2.4</v>
+      </c>
+      <c r="BN190">
+        <v>1.49</v>
+      </c>
+      <c r="BO190">
+        <v>3.05</v>
+      </c>
+      <c r="BP190">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8">
         <v>1.3</v>
@@ -3887,7 +3887,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -8213,7 +8213,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -9861,7 +9861,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR42">
         <v>1.48</v>
@@ -10476,7 +10476,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ45">
         <v>1.9</v>
@@ -15423,7 +15423,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR69">
         <v>1.13</v>
@@ -16656,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ75">
         <v>0.4</v>
@@ -19131,7 +19131,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ87">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR87">
         <v>2.14</v>
@@ -19952,7 +19952,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ91">
         <v>2</v>
@@ -22427,7 +22427,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -23866,7 +23866,7 @@
         <v>0.5</v>
       </c>
       <c r="AP110">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ110">
         <v>0.78</v>
@@ -27574,7 +27574,7 @@
         <v>2.57</v>
       </c>
       <c r="AP128">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ128">
         <v>2.09</v>
@@ -29019,7 +29019,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ135">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -31488,7 +31488,7 @@
         <v>0.86</v>
       </c>
       <c r="AP147">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ147">
         <v>0.9</v>
@@ -33551,7 +33551,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ157">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -35814,7 +35814,7 @@
         <v>1.13</v>
       </c>
       <c r="AP168">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ168">
         <v>1.11</v>
@@ -38289,7 +38289,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ180">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR180">
         <v>0.99</v>
@@ -40425,6 +40425,212 @@
       </c>
       <c r="BP190">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7465176</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45670.70833333334</v>
+      </c>
+      <c r="F191">
+        <v>19</v>
+      </c>
+      <c r="G191" t="s">
+        <v>76</v>
+      </c>
+      <c r="H191" t="s">
+        <v>79</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>154</v>
+      </c>
+      <c r="P191" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q191">
+        <v>2.6</v>
+      </c>
+      <c r="R191">
+        <v>2.1</v>
+      </c>
+      <c r="S191">
+        <v>4.33</v>
+      </c>
+      <c r="T191">
+        <v>1.4</v>
+      </c>
+      <c r="U191">
+        <v>2.75</v>
+      </c>
+      <c r="V191">
+        <v>3</v>
+      </c>
+      <c r="W191">
+        <v>1.36</v>
+      </c>
+      <c r="X191">
+        <v>8</v>
+      </c>
+      <c r="Y191">
+        <v>1.08</v>
+      </c>
+      <c r="Z191">
+        <v>1.95</v>
+      </c>
+      <c r="AA191">
+        <v>3.4</v>
+      </c>
+      <c r="AB191">
+        <v>3.9</v>
+      </c>
+      <c r="AC191">
+        <v>1.06</v>
+      </c>
+      <c r="AD191">
+        <v>10</v>
+      </c>
+      <c r="AE191">
+        <v>1.35</v>
+      </c>
+      <c r="AF191">
+        <v>3.25</v>
+      </c>
+      <c r="AG191">
+        <v>2</v>
+      </c>
+      <c r="AH191">
+        <v>1.8</v>
+      </c>
+      <c r="AI191">
+        <v>1.8</v>
+      </c>
+      <c r="AJ191">
+        <v>1.95</v>
+      </c>
+      <c r="AK191">
+        <v>1.23</v>
+      </c>
+      <c r="AL191">
+        <v>1.29</v>
+      </c>
+      <c r="AM191">
+        <v>1.87</v>
+      </c>
+      <c r="AN191">
+        <v>1.22</v>
+      </c>
+      <c r="AO191">
+        <v>1.89</v>
+      </c>
+      <c r="AP191">
+        <v>1.4</v>
+      </c>
+      <c r="AQ191">
+        <v>1.7</v>
+      </c>
+      <c r="AR191">
+        <v>1.44</v>
+      </c>
+      <c r="AS191">
+        <v>1.5</v>
+      </c>
+      <c r="AT191">
+        <v>2.94</v>
+      </c>
+      <c r="AU191">
+        <v>4</v>
+      </c>
+      <c r="AV191">
+        <v>6</v>
+      </c>
+      <c r="AW191">
+        <v>3</v>
+      </c>
+      <c r="AX191">
+        <v>10</v>
+      </c>
+      <c r="AY191">
+        <v>7</v>
+      </c>
+      <c r="AZ191">
+        <v>22</v>
+      </c>
+      <c r="BA191">
+        <v>3</v>
+      </c>
+      <c r="BB191">
+        <v>7</v>
+      </c>
+      <c r="BC191">
+        <v>10</v>
+      </c>
+      <c r="BD191">
+        <v>1.56</v>
+      </c>
+      <c r="BE191">
+        <v>6.75</v>
+      </c>
+      <c r="BF191">
+        <v>2.7</v>
+      </c>
+      <c r="BG191">
+        <v>1.26</v>
+      </c>
+      <c r="BH191">
+        <v>3.4</v>
+      </c>
+      <c r="BI191">
+        <v>1.47</v>
+      </c>
+      <c r="BJ191">
+        <v>2.48</v>
+      </c>
+      <c r="BK191">
+        <v>1.76</v>
+      </c>
+      <c r="BL191">
+        <v>1.93</v>
+      </c>
+      <c r="BM191">
+        <v>2.18</v>
+      </c>
+      <c r="BN191">
+        <v>1.58</v>
+      </c>
+      <c r="BO191">
+        <v>2.8</v>
+      </c>
+      <c r="BP191">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,15 @@
     <t>['88']</t>
   </si>
   <si>
+    <t>['31', '74']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -805,9 +814,6 @@
     <t>['20', '66']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['43', '53', '84']</t>
   </si>
   <si>
@@ -901,9 +907,6 @@
     <t>['32', '47']</t>
   </si>
   <si>
-    <t>['31', '74']</t>
-  </si>
-  <si>
     <t>['60', '90+6']</t>
   </si>
   <si>
@@ -923,6 +926,12 @@
   </si>
   <si>
     <t>['70', '86']</t>
+  </si>
+  <si>
+    <t>['59', '88']</t>
+  </si>
+  <si>
+    <t>['11', '80', '84']</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1540,7 +1549,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1824,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3">
         <v>1.2</v>
@@ -1952,7 +1961,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2033,7 +2042,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2158,7 +2167,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2239,7 +2248,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ5">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2364,7 +2373,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2570,7 +2579,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2651,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2776,7 +2785,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2982,7 +2991,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3394,7 +3403,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3475,7 +3484,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3806,7 +3815,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4502,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16">
         <v>1.56</v>
@@ -4708,7 +4717,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17">
         <v>1.3</v>
@@ -4917,7 +4926,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ18">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5120,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
         <v>1.11</v>
@@ -5660,7 +5669,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5947,7 +5956,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR23">
         <v>1.51</v>
@@ -6072,7 +6081,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6153,7 +6162,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6896,7 +6905,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6977,7 +6986,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7180,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
         <v>0.78</v>
@@ -7595,7 +7604,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ31">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -7801,7 +7810,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8004,7 +8013,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ33">
         <v>1.3</v>
@@ -8132,7 +8141,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8416,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35">
         <v>1.67</v>
@@ -8750,7 +8759,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8956,7 +8965,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9240,7 +9249,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
         <v>1.56</v>
@@ -9652,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ41">
         <v>0.9</v>
@@ -9780,7 +9789,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9986,7 +9995,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10064,10 +10073,10 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -10398,7 +10407,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10685,7 +10694,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -10810,7 +10819,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10888,10 +10897,10 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ47">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.41</v>
@@ -11016,7 +11025,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11918,7 +11927,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
         <v>0.5600000000000001</v>
@@ -12046,7 +12055,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12124,7 +12133,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ53">
         <v>1.67</v>
@@ -12333,7 +12342,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR54">
         <v>1.07</v>
@@ -12664,7 +12673,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13076,7 +13085,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13360,7 +13369,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>0.9</v>
@@ -13694,7 +13703,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13775,7 +13784,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ61">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -13981,7 +13990,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ62">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14106,7 +14115,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14184,7 +14193,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63">
         <v>1.67</v>
@@ -14518,7 +14527,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14599,7 +14608,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ65">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14724,7 +14733,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14805,7 +14814,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15008,7 +15017,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
         <v>1.3</v>
@@ -15342,7 +15351,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15420,7 +15429,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ69">
         <v>1.7</v>
@@ -15548,7 +15557,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15835,7 +15844,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -15960,7 +15969,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16244,10 +16253,10 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16784,7 +16793,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -16865,7 +16874,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ76">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR76">
         <v>1.49</v>
@@ -17277,7 +17286,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17480,7 +17489,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79">
         <v>0.11</v>
@@ -17608,7 +17617,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17814,7 +17823,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18098,7 +18107,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ82">
         <v>0.4</v>
@@ -18304,7 +18313,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
         <v>1.67</v>
@@ -18510,7 +18519,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>0.78</v>
@@ -18844,7 +18853,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19256,7 +19265,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19334,7 +19343,7 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ88">
         <v>1.67</v>
@@ -19462,7 +19471,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19543,7 +19552,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ89">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR89">
         <v>1.08</v>
@@ -19874,7 +19883,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -19955,7 +19964,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ91">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -20080,7 +20089,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20161,7 +20170,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20492,7 +20501,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20776,7 +20785,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95">
         <v>1.56</v>
@@ -20904,7 +20913,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21316,7 +21325,7 @@
         <v>163</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="Q98">
         <v>1.83</v>
@@ -21809,7 +21818,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ100">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -21934,7 +21943,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22140,7 +22149,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22218,10 +22227,10 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR102">
         <v>1.07</v>
@@ -22346,7 +22355,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22633,7 +22642,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -22964,7 +22973,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23045,7 +23054,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ106">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR106">
         <v>1.96</v>
@@ -23248,7 +23257,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ107">
         <v>0.44</v>
@@ -23454,7 +23463,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108">
         <v>0.4</v>
@@ -23660,10 +23669,10 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -23788,7 +23797,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24487,7 +24496,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ113">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24612,7 +24621,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24690,7 +24699,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ114">
         <v>0.9</v>
@@ -25024,7 +25033,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25230,7 +25239,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25436,7 +25445,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25848,7 +25857,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26341,7 +26350,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ122">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26544,10 +26553,10 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ123">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR123">
         <v>1.08</v>
@@ -26672,7 +26681,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26750,7 +26759,7 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ124">
         <v>0.44</v>
@@ -26959,7 +26968,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27162,7 +27171,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
         <v>1.2</v>
@@ -27577,7 +27586,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ128">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27780,10 +27789,10 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ129">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -27908,7 +27917,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28195,7 +28204,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ131">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28320,7 +28329,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28604,7 +28613,7 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ133">
         <v>0.11</v>
@@ -28732,7 +28741,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28813,7 +28822,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR134">
         <v>1.32</v>
@@ -28938,7 +28947,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29350,7 +29359,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29428,7 +29437,7 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ137">
         <v>1.9</v>
@@ -29762,7 +29771,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29968,7 +29977,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30458,7 +30467,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>0.44</v>
@@ -30586,7 +30595,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30667,7 +30676,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ143">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -30792,7 +30801,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31204,7 +31213,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31822,7 +31831,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -31903,7 +31912,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ149">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR149">
         <v>1.29</v>
@@ -32028,7 +32037,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32521,7 +32530,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ152">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32646,7 +32655,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32724,10 +32733,10 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ153">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR153">
         <v>1.84</v>
@@ -33058,7 +33067,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33136,7 +33145,7 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ155">
         <v>1.9</v>
@@ -33264,7 +33273,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33342,7 +33351,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ156">
         <v>1.56</v>
@@ -33676,7 +33685,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33757,7 +33766,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ158">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -33882,7 +33891,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -33963,7 +33972,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ159">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34166,7 +34175,7 @@
         <v>0.14</v>
       </c>
       <c r="AP160">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
         <v>0.11</v>
@@ -34578,7 +34587,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ162">
         <v>0.78</v>
@@ -35118,7 +35127,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35530,7 +35539,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35942,7 +35951,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36354,7 +36363,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36432,7 +36441,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ171">
         <v>0.4</v>
@@ -36844,10 +36853,10 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ173">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37050,7 +37059,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ174">
         <v>1.67</v>
@@ -37384,7 +37393,7 @@
         <v>214</v>
       </c>
       <c r="P176" t="s">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37590,7 +37599,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37671,7 +37680,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ177">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -37796,7 +37805,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37877,7 +37886,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38002,7 +38011,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38083,7 +38092,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ179">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR179">
         <v>1.81</v>
@@ -38208,7 +38217,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38286,7 +38295,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ180">
         <v>1.7</v>
@@ -38698,7 +38707,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ182">
         <v>1.3</v>
@@ -38826,7 +38835,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39238,7 +39247,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39728,7 +39737,7 @@
         <v>0.89</v>
       </c>
       <c r="AP187">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ187">
         <v>0.9</v>
@@ -40062,7 +40071,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40631,6 +40640,1036 @@
       </c>
       <c r="BP191">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7469585</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45674.70833333334</v>
+      </c>
+      <c r="F192">
+        <v>20</v>
+      </c>
+      <c r="G192" t="s">
+        <v>82</v>
+      </c>
+      <c r="H192" t="s">
+        <v>78</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>2</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>3</v>
+      </c>
+      <c r="O192" t="s">
+        <v>225</v>
+      </c>
+      <c r="P192" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q192">
+        <v>2.6</v>
+      </c>
+      <c r="R192">
+        <v>2</v>
+      </c>
+      <c r="S192">
+        <v>5</v>
+      </c>
+      <c r="T192">
+        <v>1.53</v>
+      </c>
+      <c r="U192">
+        <v>2.38</v>
+      </c>
+      <c r="V192">
+        <v>3.5</v>
+      </c>
+      <c r="W192">
+        <v>1.29</v>
+      </c>
+      <c r="X192">
+        <v>11</v>
+      </c>
+      <c r="Y192">
+        <v>1.05</v>
+      </c>
+      <c r="Z192">
+        <v>1.89</v>
+      </c>
+      <c r="AA192">
+        <v>3.39</v>
+      </c>
+      <c r="AB192">
+        <v>4.69</v>
+      </c>
+      <c r="AC192">
+        <v>1.09</v>
+      </c>
+      <c r="AD192">
+        <v>8</v>
+      </c>
+      <c r="AE192">
+        <v>1.47</v>
+      </c>
+      <c r="AF192">
+        <v>2.7</v>
+      </c>
+      <c r="AG192">
+        <v>2.5</v>
+      </c>
+      <c r="AH192">
+        <v>1.53</v>
+      </c>
+      <c r="AI192">
+        <v>2.1</v>
+      </c>
+      <c r="AJ192">
+        <v>1.67</v>
+      </c>
+      <c r="AK192">
+        <v>1.2</v>
+      </c>
+      <c r="AL192">
+        <v>1.32</v>
+      </c>
+      <c r="AM192">
+        <v>1.88</v>
+      </c>
+      <c r="AN192">
+        <v>1.5</v>
+      </c>
+      <c r="AO192">
+        <v>0.33</v>
+      </c>
+      <c r="AP192">
+        <v>1.64</v>
+      </c>
+      <c r="AQ192">
+        <v>0.3</v>
+      </c>
+      <c r="AR192">
+        <v>1.16</v>
+      </c>
+      <c r="AS192">
+        <v>0.89</v>
+      </c>
+      <c r="AT192">
+        <v>2.05</v>
+      </c>
+      <c r="AU192">
+        <v>5</v>
+      </c>
+      <c r="AV192">
+        <v>5</v>
+      </c>
+      <c r="AW192">
+        <v>8</v>
+      </c>
+      <c r="AX192">
+        <v>7</v>
+      </c>
+      <c r="AY192">
+        <v>16</v>
+      </c>
+      <c r="AZ192">
+        <v>14</v>
+      </c>
+      <c r="BA192">
+        <v>1</v>
+      </c>
+      <c r="BB192">
+        <v>7</v>
+      </c>
+      <c r="BC192">
+        <v>8</v>
+      </c>
+      <c r="BD192">
+        <v>1.54</v>
+      </c>
+      <c r="BE192">
+        <v>6.75</v>
+      </c>
+      <c r="BF192">
+        <v>2.7</v>
+      </c>
+      <c r="BG192">
+        <v>1.4</v>
+      </c>
+      <c r="BH192">
+        <v>2.65</v>
+      </c>
+      <c r="BI192">
+        <v>1.67</v>
+      </c>
+      <c r="BJ192">
+        <v>2.05</v>
+      </c>
+      <c r="BK192">
+        <v>2.08</v>
+      </c>
+      <c r="BL192">
+        <v>1.65</v>
+      </c>
+      <c r="BM192">
+        <v>2.7</v>
+      </c>
+      <c r="BN192">
+        <v>1.4</v>
+      </c>
+      <c r="BO192">
+        <v>3.55</v>
+      </c>
+      <c r="BP192">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7465183</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45675.41666666666</v>
+      </c>
+      <c r="F193">
+        <v>20</v>
+      </c>
+      <c r="G193" t="s">
+        <v>89</v>
+      </c>
+      <c r="H193" t="s">
+        <v>80</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" t="s">
+        <v>128</v>
+      </c>
+      <c r="P193" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q193">
+        <v>2.5</v>
+      </c>
+      <c r="R193">
+        <v>2.2</v>
+      </c>
+      <c r="S193">
+        <v>4.5</v>
+      </c>
+      <c r="T193">
+        <v>1.4</v>
+      </c>
+      <c r="U193">
+        <v>2.75</v>
+      </c>
+      <c r="V193">
+        <v>3</v>
+      </c>
+      <c r="W193">
+        <v>1.36</v>
+      </c>
+      <c r="X193">
+        <v>8</v>
+      </c>
+      <c r="Y193">
+        <v>1.08</v>
+      </c>
+      <c r="Z193">
+        <v>1.91</v>
+      </c>
+      <c r="AA193">
+        <v>3.74</v>
+      </c>
+      <c r="AB193">
+        <v>4.11</v>
+      </c>
+      <c r="AC193">
+        <v>1.05</v>
+      </c>
+      <c r="AD193">
+        <v>12</v>
+      </c>
+      <c r="AE193">
+        <v>1.32</v>
+      </c>
+      <c r="AF193">
+        <v>3.4</v>
+      </c>
+      <c r="AG193">
+        <v>1.98</v>
+      </c>
+      <c r="AH193">
+        <v>1.91</v>
+      </c>
+      <c r="AI193">
+        <v>1.8</v>
+      </c>
+      <c r="AJ193">
+        <v>1.95</v>
+      </c>
+      <c r="AK193">
+        <v>1.23</v>
+      </c>
+      <c r="AL193">
+        <v>1.28</v>
+      </c>
+      <c r="AM193">
+        <v>1.9</v>
+      </c>
+      <c r="AN193">
+        <v>1.78</v>
+      </c>
+      <c r="AO193">
+        <v>0.67</v>
+      </c>
+      <c r="AP193">
+        <v>1.6</v>
+      </c>
+      <c r="AQ193">
+        <v>0.9</v>
+      </c>
+      <c r="AR193">
+        <v>1.37</v>
+      </c>
+      <c r="AS193">
+        <v>1.15</v>
+      </c>
+      <c r="AT193">
+        <v>2.52</v>
+      </c>
+      <c r="AU193">
+        <v>5</v>
+      </c>
+      <c r="AV193">
+        <v>7</v>
+      </c>
+      <c r="AW193">
+        <v>3</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>8</v>
+      </c>
+      <c r="AZ193">
+        <v>15</v>
+      </c>
+      <c r="BA193">
+        <v>7</v>
+      </c>
+      <c r="BB193">
+        <v>4</v>
+      </c>
+      <c r="BC193">
+        <v>11</v>
+      </c>
+      <c r="BD193">
+        <v>1.54</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.7</v>
+      </c>
+      <c r="BG193">
+        <v>1.37</v>
+      </c>
+      <c r="BH193">
+        <v>2.8</v>
+      </c>
+      <c r="BI193">
+        <v>1.64</v>
+      </c>
+      <c r="BJ193">
+        <v>2.1</v>
+      </c>
+      <c r="BK193">
+        <v>2.02</v>
+      </c>
+      <c r="BL193">
+        <v>1.68</v>
+      </c>
+      <c r="BM193">
+        <v>2.55</v>
+      </c>
+      <c r="BN193">
+        <v>1.43</v>
+      </c>
+      <c r="BO193">
+        <v>3.4</v>
+      </c>
+      <c r="BP193">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7465186</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45675.51041666666</v>
+      </c>
+      <c r="F194">
+        <v>20</v>
+      </c>
+      <c r="G194" t="s">
+        <v>85</v>
+      </c>
+      <c r="H194" t="s">
+        <v>87</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
+        <v>226</v>
+      </c>
+      <c r="P194" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q194">
+        <v>7.5</v>
+      </c>
+      <c r="R194">
+        <v>2.2</v>
+      </c>
+      <c r="S194">
+        <v>2.05</v>
+      </c>
+      <c r="T194">
+        <v>1.44</v>
+      </c>
+      <c r="U194">
+        <v>2.63</v>
+      </c>
+      <c r="V194">
+        <v>3</v>
+      </c>
+      <c r="W194">
+        <v>1.36</v>
+      </c>
+      <c r="X194">
+        <v>9</v>
+      </c>
+      <c r="Y194">
+        <v>1.07</v>
+      </c>
+      <c r="Z194">
+        <v>7.53</v>
+      </c>
+      <c r="AA194">
+        <v>4.33</v>
+      </c>
+      <c r="AB194">
+        <v>1.48</v>
+      </c>
+      <c r="AC194">
+        <v>1.06</v>
+      </c>
+      <c r="AD194">
+        <v>10</v>
+      </c>
+      <c r="AE194">
+        <v>1.36</v>
+      </c>
+      <c r="AF194">
+        <v>3.2</v>
+      </c>
+      <c r="AG194">
+        <v>2</v>
+      </c>
+      <c r="AH194">
+        <v>1.8</v>
+      </c>
+      <c r="AI194">
+        <v>2.2</v>
+      </c>
+      <c r="AJ194">
+        <v>1.62</v>
+      </c>
+      <c r="AK194">
+        <v>2.65</v>
+      </c>
+      <c r="AL194">
+        <v>1.22</v>
+      </c>
+      <c r="AM194">
+        <v>1.1</v>
+      </c>
+      <c r="AN194">
+        <v>1.11</v>
+      </c>
+      <c r="AO194">
+        <v>2</v>
+      </c>
+      <c r="AP194">
+        <v>1.3</v>
+      </c>
+      <c r="AQ194">
+        <v>1.8</v>
+      </c>
+      <c r="AR194">
+        <v>0.96</v>
+      </c>
+      <c r="AS194">
+        <v>1.06</v>
+      </c>
+      <c r="AT194">
+        <v>2.02</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>5</v>
+      </c>
+      <c r="AW194">
+        <v>6</v>
+      </c>
+      <c r="AX194">
+        <v>15</v>
+      </c>
+      <c r="AY194">
+        <v>11</v>
+      </c>
+      <c r="AZ194">
+        <v>22</v>
+      </c>
+      <c r="BA194">
+        <v>2</v>
+      </c>
+      <c r="BB194">
+        <v>9</v>
+      </c>
+      <c r="BC194">
+        <v>11</v>
+      </c>
+      <c r="BD194">
+        <v>3.05</v>
+      </c>
+      <c r="BE194">
+        <v>6.5</v>
+      </c>
+      <c r="BF194">
+        <v>1.48</v>
+      </c>
+      <c r="BG194">
+        <v>1.44</v>
+      </c>
+      <c r="BH194">
+        <v>2.55</v>
+      </c>
+      <c r="BI194">
+        <v>1.73</v>
+      </c>
+      <c r="BJ194">
+        <v>1.97</v>
+      </c>
+      <c r="BK194">
+        <v>2.18</v>
+      </c>
+      <c r="BL194">
+        <v>1.58</v>
+      </c>
+      <c r="BM194">
+        <v>2.8</v>
+      </c>
+      <c r="BN194">
+        <v>1.36</v>
+      </c>
+      <c r="BO194">
+        <v>3.8</v>
+      </c>
+      <c r="BP194">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7465191</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F195">
+        <v>20</v>
+      </c>
+      <c r="G195" t="s">
+        <v>71</v>
+      </c>
+      <c r="H195" t="s">
+        <v>86</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>3</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195" t="s">
+        <v>187</v>
+      </c>
+      <c r="P195" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q195">
+        <v>2.38</v>
+      </c>
+      <c r="R195">
+        <v>2.1</v>
+      </c>
+      <c r="S195">
+        <v>5.5</v>
+      </c>
+      <c r="T195">
+        <v>1.44</v>
+      </c>
+      <c r="U195">
+        <v>2.63</v>
+      </c>
+      <c r="V195">
+        <v>3.25</v>
+      </c>
+      <c r="W195">
+        <v>1.33</v>
+      </c>
+      <c r="X195">
+        <v>9</v>
+      </c>
+      <c r="Y195">
+        <v>1.07</v>
+      </c>
+      <c r="Z195">
+        <v>1.76</v>
+      </c>
+      <c r="AA195">
+        <v>3.82</v>
+      </c>
+      <c r="AB195">
+        <v>4.85</v>
+      </c>
+      <c r="AC195">
+        <v>1.06</v>
+      </c>
+      <c r="AD195">
+        <v>10</v>
+      </c>
+      <c r="AE195">
+        <v>1.38</v>
+      </c>
+      <c r="AF195">
+        <v>3.1</v>
+      </c>
+      <c r="AG195">
+        <v>2.1</v>
+      </c>
+      <c r="AH195">
+        <v>1.73</v>
+      </c>
+      <c r="AI195">
+        <v>2</v>
+      </c>
+      <c r="AJ195">
+        <v>1.75</v>
+      </c>
+      <c r="AK195">
+        <v>1.17</v>
+      </c>
+      <c r="AL195">
+        <v>1.27</v>
+      </c>
+      <c r="AM195">
+        <v>2.1</v>
+      </c>
+      <c r="AN195">
+        <v>1.78</v>
+      </c>
+      <c r="AO195">
+        <v>0.5</v>
+      </c>
+      <c r="AP195">
+        <v>1.6</v>
+      </c>
+      <c r="AQ195">
+        <v>0.73</v>
+      </c>
+      <c r="AR195">
+        <v>1.78</v>
+      </c>
+      <c r="AS195">
+        <v>1.15</v>
+      </c>
+      <c r="AT195">
+        <v>2.93</v>
+      </c>
+      <c r="AU195">
+        <v>4</v>
+      </c>
+      <c r="AV195">
+        <v>6</v>
+      </c>
+      <c r="AW195">
+        <v>5</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>13</v>
+      </c>
+      <c r="AZ195">
+        <v>13</v>
+      </c>
+      <c r="BA195">
+        <v>2</v>
+      </c>
+      <c r="BB195">
+        <v>3</v>
+      </c>
+      <c r="BC195">
+        <v>5</v>
+      </c>
+      <c r="BD195">
+        <v>1.44</v>
+      </c>
+      <c r="BE195">
+        <v>6.75</v>
+      </c>
+      <c r="BF195">
+        <v>3.15</v>
+      </c>
+      <c r="BG195">
+        <v>1.37</v>
+      </c>
+      <c r="BH195">
+        <v>2.8</v>
+      </c>
+      <c r="BI195">
+        <v>1.64</v>
+      </c>
+      <c r="BJ195">
+        <v>2.1</v>
+      </c>
+      <c r="BK195">
+        <v>2</v>
+      </c>
+      <c r="BL195">
+        <v>1.71</v>
+      </c>
+      <c r="BM195">
+        <v>2.55</v>
+      </c>
+      <c r="BN195">
+        <v>1.44</v>
+      </c>
+      <c r="BO195">
+        <v>3.3</v>
+      </c>
+      <c r="BP195">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7465187</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45675.70833333334</v>
+      </c>
+      <c r="F196">
+        <v>20</v>
+      </c>
+      <c r="G196" t="s">
+        <v>83</v>
+      </c>
+      <c r="H196" t="s">
+        <v>81</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>2</v>
+      </c>
+      <c r="O196" t="s">
+        <v>227</v>
+      </c>
+      <c r="P196" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q196">
+        <v>6.5</v>
+      </c>
+      <c r="R196">
+        <v>2.38</v>
+      </c>
+      <c r="S196">
+        <v>2</v>
+      </c>
+      <c r="T196">
+        <v>1.36</v>
+      </c>
+      <c r="U196">
+        <v>3</v>
+      </c>
+      <c r="V196">
+        <v>2.63</v>
+      </c>
+      <c r="W196">
+        <v>1.44</v>
+      </c>
+      <c r="X196">
+        <v>7</v>
+      </c>
+      <c r="Y196">
+        <v>1.1</v>
+      </c>
+      <c r="Z196">
+        <v>7.08</v>
+      </c>
+      <c r="AA196">
+        <v>4.52</v>
+      </c>
+      <c r="AB196">
+        <v>1.48</v>
+      </c>
+      <c r="AC196">
+        <v>1.04</v>
+      </c>
+      <c r="AD196">
+        <v>13</v>
+      </c>
+      <c r="AE196">
+        <v>1.26</v>
+      </c>
+      <c r="AF196">
+        <v>4</v>
+      </c>
+      <c r="AG196">
+        <v>1.8</v>
+      </c>
+      <c r="AH196">
+        <v>2</v>
+      </c>
+      <c r="AI196">
+        <v>1.95</v>
+      </c>
+      <c r="AJ196">
+        <v>1.8</v>
+      </c>
+      <c r="AK196">
+        <v>2.5</v>
+      </c>
+      <c r="AL196">
+        <v>1.21</v>
+      </c>
+      <c r="AM196">
+        <v>1.12</v>
+      </c>
+      <c r="AN196">
+        <v>1.4</v>
+      </c>
+      <c r="AO196">
+        <v>2.09</v>
+      </c>
+      <c r="AP196">
+        <v>1.36</v>
+      </c>
+      <c r="AQ196">
+        <v>2</v>
+      </c>
+      <c r="AR196">
+        <v>1.38</v>
+      </c>
+      <c r="AS196">
+        <v>1.64</v>
+      </c>
+      <c r="AT196">
+        <v>3.02</v>
+      </c>
+      <c r="AU196">
+        <v>5</v>
+      </c>
+      <c r="AV196">
+        <v>6</v>
+      </c>
+      <c r="AW196">
+        <v>5</v>
+      </c>
+      <c r="AX196">
+        <v>16</v>
+      </c>
+      <c r="AY196">
+        <v>12</v>
+      </c>
+      <c r="AZ196">
+        <v>28</v>
+      </c>
+      <c r="BA196">
+        <v>2</v>
+      </c>
+      <c r="BB196">
+        <v>10</v>
+      </c>
+      <c r="BC196">
+        <v>12</v>
+      </c>
+      <c r="BD196">
+        <v>3.3</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>1.43</v>
+      </c>
+      <c r="BG196">
+        <v>1.4</v>
+      </c>
+      <c r="BH196">
+        <v>2.7</v>
+      </c>
+      <c r="BI196">
+        <v>1.67</v>
+      </c>
+      <c r="BJ196">
+        <v>2.05</v>
+      </c>
+      <c r="BK196">
+        <v>2.07</v>
+      </c>
+      <c r="BL196">
+        <v>1.65</v>
+      </c>
+      <c r="BM196">
+        <v>2.65</v>
+      </c>
+      <c r="BN196">
+        <v>1.41</v>
+      </c>
+      <c r="BO196">
+        <v>3.45</v>
+      </c>
+      <c r="BP196">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,12 @@
     <t>['34']</t>
   </si>
   <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['18', '33', '36', '57']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -932,6 +938,9 @@
   </si>
   <si>
     <t>['11', '80', '84']</t>
+  </si>
+  <si>
+    <t>['62', '71']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1558,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1961,7 +1970,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2039,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4">
         <v>0.73</v>
@@ -2167,7 +2176,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2373,7 +2382,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2451,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6">
         <v>0.9</v>
@@ -2579,7 +2588,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2657,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2785,7 +2794,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2866,7 +2875,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2991,7 +3000,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3403,7 +3412,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3687,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>0.4</v>
@@ -3815,7 +3824,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4099,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ14">
         <v>1.67</v>
@@ -4308,7 +4317,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ15">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4514,7 +4523,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ16">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4720,7 +4729,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4923,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ18">
         <v>0.3</v>
@@ -5132,7 +5141,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5669,7 +5678,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6081,7 +6090,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6905,7 +6914,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8016,7 +8025,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ33">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -8141,7 +8150,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8219,7 +8228,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34">
         <v>1.7</v>
@@ -8634,7 +8643,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -8759,7 +8768,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8837,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ37">
         <v>0.44</v>
@@ -8965,7 +8974,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9252,7 +9261,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -9455,7 +9464,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ40">
         <v>0.9</v>
@@ -9789,7 +9798,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9995,7 +10004,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10407,7 +10416,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10691,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46">
         <v>0.3</v>
@@ -10819,7 +10828,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11025,7 +11034,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11106,7 +11115,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11724,7 +11733,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -12055,7 +12064,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12136,7 +12145,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ53">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12548,7 +12557,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ55">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12673,7 +12682,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12751,10 +12760,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -12957,7 +12966,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ57">
         <v>1.2</v>
@@ -13085,7 +13094,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13163,7 +13172,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ58">
         <v>0.11</v>
@@ -13703,7 +13712,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14115,7 +14124,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14399,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64">
         <v>0.78</v>
@@ -14527,7 +14536,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14733,7 +14742,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14811,7 +14820,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ66">
         <v>0.73</v>
@@ -15020,7 +15029,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR67">
         <v>1.32</v>
@@ -15351,7 +15360,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15557,7 +15566,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15841,7 +15850,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ71">
         <v>1.8</v>
@@ -15969,7 +15978,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16793,7 +16802,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -16871,7 +16880,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76">
         <v>2</v>
@@ -17077,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17617,7 +17626,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17823,7 +17832,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17904,7 +17913,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ81">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -18853,7 +18862,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -18934,7 +18943,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -19137,7 +19146,7 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ87">
         <v>1.7</v>
@@ -19265,7 +19274,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19346,7 +19355,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19471,7 +19480,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19883,7 +19892,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20089,7 +20098,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20501,7 +20510,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20579,7 +20588,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94">
         <v>0.9</v>
@@ -20788,7 +20797,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ95">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -20913,7 +20922,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -20991,7 +21000,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96">
         <v>1.9</v>
@@ -21200,7 +21209,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ97">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21943,7 +21952,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22021,10 +22030,10 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ101">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -22149,7 +22158,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22355,7 +22364,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22973,7 +22982,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23051,7 +23060,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ106">
         <v>2</v>
@@ -23797,7 +23806,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24084,7 +24093,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24493,7 +24502,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ113">
         <v>0.3</v>
@@ -24621,7 +24630,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24908,7 +24917,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ115">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25033,7 +25042,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25239,7 +25248,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25320,7 +25329,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25445,7 +25454,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25729,7 +25738,7 @@
         <v>0.4</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ119">
         <v>0.5600000000000001</v>
@@ -25857,7 +25866,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25938,7 +25947,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -26141,7 +26150,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ121">
         <v>0.78</v>
@@ -26681,7 +26690,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27380,7 +27389,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27917,7 +27926,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -27995,7 +28004,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ130">
         <v>0.9</v>
@@ -28329,7 +28338,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28741,7 +28750,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28819,7 +28828,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134">
         <v>2</v>
@@ -28947,7 +28956,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29025,7 +29034,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.7</v>
@@ -29234,7 +29243,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ136">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR136">
         <v>1.38</v>
@@ -29359,7 +29368,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29646,7 +29655,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ138">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -29771,7 +29780,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29977,7 +29986,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30058,7 +30067,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ140">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -30595,7 +30604,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30801,7 +30810,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31085,7 +31094,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ145">
         <v>0.5600000000000001</v>
@@ -31213,7 +31222,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31294,7 +31303,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31831,7 +31840,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32037,7 +32046,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32321,7 +32330,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ151">
         <v>1.67</v>
@@ -32655,7 +32664,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32939,10 +32948,10 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ154">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.29</v>
@@ -33067,7 +33076,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33273,7 +33282,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33354,7 +33363,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ156">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -33685,7 +33694,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33763,7 +33772,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ158">
         <v>0.73</v>
@@ -33891,7 +33900,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35127,7 +35136,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35539,7 +35548,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35620,7 +35629,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ167">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -35826,7 +35835,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ168">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -35951,7 +35960,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36363,7 +36372,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36650,7 +36659,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ172">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR172">
         <v>1.52</v>
@@ -37265,10 +37274,10 @@
         <v>1.75</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ175">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37471,10 +37480,10 @@
         <v>1.5</v>
       </c>
       <c r="AP176">
+        <v>1.73</v>
+      </c>
+      <c r="AQ176">
         <v>1.8</v>
-      </c>
-      <c r="AQ176">
-        <v>1.67</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37599,7 +37608,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37805,7 +37814,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37883,7 +37892,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ178">
         <v>0.73</v>
@@ -38011,7 +38020,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38089,7 +38098,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ179">
         <v>0.9</v>
@@ -38217,7 +38226,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38710,7 +38719,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ182">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR182">
         <v>1.81</v>
@@ -38835,7 +38844,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -38913,7 +38922,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ183">
         <v>1.9</v>
@@ -39247,7 +39256,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40071,7 +40080,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40895,7 +40904,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41307,7 +41316,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41670,6 +41679,830 @@
       </c>
       <c r="BP196">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7465185</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45676.41666666666</v>
+      </c>
+      <c r="F197">
+        <v>20</v>
+      </c>
+      <c r="G197" t="s">
+        <v>72</v>
+      </c>
+      <c r="H197" t="s">
+        <v>70</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
+      <c r="N197">
+        <v>3</v>
+      </c>
+      <c r="O197" t="s">
+        <v>228</v>
+      </c>
+      <c r="P197" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q197">
+        <v>3.5</v>
+      </c>
+      <c r="R197">
+        <v>1.95</v>
+      </c>
+      <c r="S197">
+        <v>3.5</v>
+      </c>
+      <c r="T197">
+        <v>1.53</v>
+      </c>
+      <c r="U197">
+        <v>2.38</v>
+      </c>
+      <c r="V197">
+        <v>3.5</v>
+      </c>
+      <c r="W197">
+        <v>1.29</v>
+      </c>
+      <c r="X197">
+        <v>11</v>
+      </c>
+      <c r="Y197">
+        <v>1.05</v>
+      </c>
+      <c r="Z197">
+        <v>2.75</v>
+      </c>
+      <c r="AA197">
+        <v>3.08</v>
+      </c>
+      <c r="AB197">
+        <v>2.77</v>
+      </c>
+      <c r="AC197">
+        <v>1.09</v>
+      </c>
+      <c r="AD197">
+        <v>8</v>
+      </c>
+      <c r="AE197">
+        <v>1.45</v>
+      </c>
+      <c r="AF197">
+        <v>2.75</v>
+      </c>
+      <c r="AG197">
+        <v>2.38</v>
+      </c>
+      <c r="AH197">
+        <v>1.57</v>
+      </c>
+      <c r="AI197">
+        <v>1.95</v>
+      </c>
+      <c r="AJ197">
+        <v>1.8</v>
+      </c>
+      <c r="AK197">
+        <v>1.47</v>
+      </c>
+      <c r="AL197">
+        <v>1.32</v>
+      </c>
+      <c r="AM197">
+        <v>1.48</v>
+      </c>
+      <c r="AN197">
+        <v>2</v>
+      </c>
+      <c r="AO197">
+        <v>1.67</v>
+      </c>
+      <c r="AP197">
+        <v>1.82</v>
+      </c>
+      <c r="AQ197">
+        <v>1.8</v>
+      </c>
+      <c r="AR197">
+        <v>1.41</v>
+      </c>
+      <c r="AS197">
+        <v>1.34</v>
+      </c>
+      <c r="AT197">
+        <v>2.75</v>
+      </c>
+      <c r="AU197">
+        <v>2</v>
+      </c>
+      <c r="AV197">
+        <v>7</v>
+      </c>
+      <c r="AW197">
+        <v>2</v>
+      </c>
+      <c r="AX197">
+        <v>5</v>
+      </c>
+      <c r="AY197">
+        <v>4</v>
+      </c>
+      <c r="AZ197">
+        <v>15</v>
+      </c>
+      <c r="BA197">
+        <v>3</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>7</v>
+      </c>
+      <c r="BD197">
+        <v>2.05</v>
+      </c>
+      <c r="BE197">
+        <v>6.4</v>
+      </c>
+      <c r="BF197">
+        <v>1.96</v>
+      </c>
+      <c r="BG197">
+        <v>1.38</v>
+      </c>
+      <c r="BH197">
+        <v>2.7</v>
+      </c>
+      <c r="BI197">
+        <v>1.65</v>
+      </c>
+      <c r="BJ197">
+        <v>2.08</v>
+      </c>
+      <c r="BK197">
+        <v>2.05</v>
+      </c>
+      <c r="BL197">
+        <v>1.67</v>
+      </c>
+      <c r="BM197">
+        <v>2.63</v>
+      </c>
+      <c r="BN197">
+        <v>1.41</v>
+      </c>
+      <c r="BO197">
+        <v>3.45</v>
+      </c>
+      <c r="BP197">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7465190</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45676.51041666666</v>
+      </c>
+      <c r="F198">
+        <v>20</v>
+      </c>
+      <c r="G198" t="s">
+        <v>84</v>
+      </c>
+      <c r="H198" t="s">
+        <v>73</v>
+      </c>
+      <c r="I198">
+        <v>3</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>4</v>
+      </c>
+      <c r="L198">
+        <v>4</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>5</v>
+      </c>
+      <c r="O198" t="s">
+        <v>229</v>
+      </c>
+      <c r="P198" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q198">
+        <v>1.44</v>
+      </c>
+      <c r="R198">
+        <v>3.25</v>
+      </c>
+      <c r="S198">
+        <v>10</v>
+      </c>
+      <c r="T198">
+        <v>1.17</v>
+      </c>
+      <c r="U198">
+        <v>5</v>
+      </c>
+      <c r="V198">
+        <v>1.83</v>
+      </c>
+      <c r="W198">
+        <v>1.83</v>
+      </c>
+      <c r="X198">
+        <v>3.75</v>
+      </c>
+      <c r="Y198">
+        <v>1.25</v>
+      </c>
+      <c r="Z198">
+        <v>1.14</v>
+      </c>
+      <c r="AA198">
+        <v>8</v>
+      </c>
+      <c r="AB198">
+        <v>15</v>
+      </c>
+      <c r="AC198">
+        <v>1.01</v>
+      </c>
+      <c r="AD198">
+        <v>34</v>
+      </c>
+      <c r="AE198">
+        <v>1.08</v>
+      </c>
+      <c r="AF198">
+        <v>8</v>
+      </c>
+      <c r="AG198">
+        <v>1.3</v>
+      </c>
+      <c r="AH198">
+        <v>3.5</v>
+      </c>
+      <c r="AI198">
+        <v>1.91</v>
+      </c>
+      <c r="AJ198">
+        <v>1.91</v>
+      </c>
+      <c r="AK198">
+        <v>1.02</v>
+      </c>
+      <c r="AL198">
+        <v>1.07</v>
+      </c>
+      <c r="AM198">
+        <v>5.25</v>
+      </c>
+      <c r="AN198">
+        <v>2.67</v>
+      </c>
+      <c r="AO198">
+        <v>1.11</v>
+      </c>
+      <c r="AP198">
+        <v>2.7</v>
+      </c>
+      <c r="AQ198">
+        <v>1</v>
+      </c>
+      <c r="AR198">
+        <v>1.8</v>
+      </c>
+      <c r="AS198">
+        <v>1.06</v>
+      </c>
+      <c r="AT198">
+        <v>2.86</v>
+      </c>
+      <c r="AU198">
+        <v>14</v>
+      </c>
+      <c r="AV198">
+        <v>3</v>
+      </c>
+      <c r="AW198">
+        <v>12</v>
+      </c>
+      <c r="AX198">
+        <v>4</v>
+      </c>
+      <c r="AY198">
+        <v>27</v>
+      </c>
+      <c r="AZ198">
+        <v>8</v>
+      </c>
+      <c r="BA198">
+        <v>8</v>
+      </c>
+      <c r="BB198">
+        <v>2</v>
+      </c>
+      <c r="BC198">
+        <v>10</v>
+      </c>
+      <c r="BD198">
+        <v>1.14</v>
+      </c>
+      <c r="BE198">
+        <v>10</v>
+      </c>
+      <c r="BF198">
+        <v>5.8</v>
+      </c>
+      <c r="BG198">
+        <v>1.22</v>
+      </c>
+      <c r="BH198">
+        <v>3.65</v>
+      </c>
+      <c r="BI198">
+        <v>1.41</v>
+      </c>
+      <c r="BJ198">
+        <v>2.65</v>
+      </c>
+      <c r="BK198">
+        <v>1.66</v>
+      </c>
+      <c r="BL198">
+        <v>2.07</v>
+      </c>
+      <c r="BM198">
+        <v>2.02</v>
+      </c>
+      <c r="BN198">
+        <v>1.68</v>
+      </c>
+      <c r="BO198">
+        <v>2.55</v>
+      </c>
+      <c r="BP198">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7465184</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45676.60416666666</v>
+      </c>
+      <c r="F199">
+        <v>20</v>
+      </c>
+      <c r="G199" t="s">
+        <v>74</v>
+      </c>
+      <c r="H199" t="s">
+        <v>88</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>161</v>
+      </c>
+      <c r="P199" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q199">
+        <v>3.1</v>
+      </c>
+      <c r="R199">
+        <v>1.95</v>
+      </c>
+      <c r="S199">
+        <v>4.33</v>
+      </c>
+      <c r="T199">
+        <v>1.57</v>
+      </c>
+      <c r="U199">
+        <v>2.25</v>
+      </c>
+      <c r="V199">
+        <v>3.75</v>
+      </c>
+      <c r="W199">
+        <v>1.25</v>
+      </c>
+      <c r="X199">
+        <v>11</v>
+      </c>
+      <c r="Y199">
+        <v>1.05</v>
+      </c>
+      <c r="Z199">
+        <v>2.23</v>
+      </c>
+      <c r="AA199">
+        <v>3.12</v>
+      </c>
+      <c r="AB199">
+        <v>3.57</v>
+      </c>
+      <c r="AC199">
+        <v>1.1</v>
+      </c>
+      <c r="AD199">
+        <v>7.5</v>
+      </c>
+      <c r="AE199">
+        <v>1.5</v>
+      </c>
+      <c r="AF199">
+        <v>2.45</v>
+      </c>
+      <c r="AG199">
+        <v>2.5</v>
+      </c>
+      <c r="AH199">
+        <v>1.53</v>
+      </c>
+      <c r="AI199">
+        <v>2.05</v>
+      </c>
+      <c r="AJ199">
+        <v>1.7</v>
+      </c>
+      <c r="AK199">
+        <v>1.3</v>
+      </c>
+      <c r="AL199">
+        <v>1.32</v>
+      </c>
+      <c r="AM199">
+        <v>1.68</v>
+      </c>
+      <c r="AN199">
+        <v>1.8</v>
+      </c>
+      <c r="AO199">
+        <v>1.3</v>
+      </c>
+      <c r="AP199">
+        <v>1.73</v>
+      </c>
+      <c r="AQ199">
+        <v>1.27</v>
+      </c>
+      <c r="AR199">
+        <v>1.47</v>
+      </c>
+      <c r="AS199">
+        <v>1.05</v>
+      </c>
+      <c r="AT199">
+        <v>2.52</v>
+      </c>
+      <c r="AU199">
+        <v>4</v>
+      </c>
+      <c r="AV199">
+        <v>4</v>
+      </c>
+      <c r="AW199">
+        <v>9</v>
+      </c>
+      <c r="AX199">
+        <v>5</v>
+      </c>
+      <c r="AY199">
+        <v>17</v>
+      </c>
+      <c r="AZ199">
+        <v>10</v>
+      </c>
+      <c r="BA199">
+        <v>6</v>
+      </c>
+      <c r="BB199">
+        <v>3</v>
+      </c>
+      <c r="BC199">
+        <v>9</v>
+      </c>
+      <c r="BD199">
+        <v>1.77</v>
+      </c>
+      <c r="BE199">
+        <v>6.5</v>
+      </c>
+      <c r="BF199">
+        <v>2.23</v>
+      </c>
+      <c r="BG199">
+        <v>1.32</v>
+      </c>
+      <c r="BH199">
+        <v>3.05</v>
+      </c>
+      <c r="BI199">
+        <v>1.55</v>
+      </c>
+      <c r="BJ199">
+        <v>2.25</v>
+      </c>
+      <c r="BK199">
+        <v>1.9</v>
+      </c>
+      <c r="BL199">
+        <v>1.79</v>
+      </c>
+      <c r="BM199">
+        <v>2.38</v>
+      </c>
+      <c r="BN199">
+        <v>1.5</v>
+      </c>
+      <c r="BO199">
+        <v>3.1</v>
+      </c>
+      <c r="BP199">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7465189</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45676.70833333334</v>
+      </c>
+      <c r="F200">
+        <v>20</v>
+      </c>
+      <c r="G200" t="s">
+        <v>75</v>
+      </c>
+      <c r="H200" t="s">
+        <v>76</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
+        <v>188</v>
+      </c>
+      <c r="P200" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q200">
+        <v>4</v>
+      </c>
+      <c r="R200">
+        <v>1.83</v>
+      </c>
+      <c r="S200">
+        <v>3.5</v>
+      </c>
+      <c r="T200">
+        <v>1.67</v>
+      </c>
+      <c r="U200">
+        <v>2.1</v>
+      </c>
+      <c r="V200">
+        <v>4</v>
+      </c>
+      <c r="W200">
+        <v>1.22</v>
+      </c>
+      <c r="X200">
+        <v>15</v>
+      </c>
+      <c r="Y200">
+        <v>1.03</v>
+      </c>
+      <c r="Z200">
+        <v>3</v>
+      </c>
+      <c r="AA200">
+        <v>3</v>
+      </c>
+      <c r="AB200">
+        <v>2.5</v>
+      </c>
+      <c r="AC200">
+        <v>1.12</v>
+      </c>
+      <c r="AD200">
+        <v>6.5</v>
+      </c>
+      <c r="AE200">
+        <v>1.57</v>
+      </c>
+      <c r="AF200">
+        <v>2.25</v>
+      </c>
+      <c r="AG200">
+        <v>3</v>
+      </c>
+      <c r="AH200">
+        <v>1.4</v>
+      </c>
+      <c r="AI200">
+        <v>2.25</v>
+      </c>
+      <c r="AJ200">
+        <v>1.57</v>
+      </c>
+      <c r="AK200">
+        <v>1.51</v>
+      </c>
+      <c r="AL200">
+        <v>1.38</v>
+      </c>
+      <c r="AM200">
+        <v>1.35</v>
+      </c>
+      <c r="AN200">
+        <v>1</v>
+      </c>
+      <c r="AO200">
+        <v>1.56</v>
+      </c>
+      <c r="AP200">
+        <v>1.2</v>
+      </c>
+      <c r="AQ200">
+        <v>1.4</v>
+      </c>
+      <c r="AR200">
+        <v>1.33</v>
+      </c>
+      <c r="AS200">
+        <v>1.03</v>
+      </c>
+      <c r="AT200">
+        <v>2.36</v>
+      </c>
+      <c r="AU200">
+        <v>3</v>
+      </c>
+      <c r="AV200">
+        <v>4</v>
+      </c>
+      <c r="AW200">
+        <v>5</v>
+      </c>
+      <c r="AX200">
+        <v>6</v>
+      </c>
+      <c r="AY200">
+        <v>9</v>
+      </c>
+      <c r="AZ200">
+        <v>13</v>
+      </c>
+      <c r="BA200">
+        <v>4</v>
+      </c>
+      <c r="BB200">
+        <v>7</v>
+      </c>
+      <c r="BC200">
+        <v>11</v>
+      </c>
+      <c r="BD200">
+        <v>1.93</v>
+      </c>
+      <c r="BE200">
+        <v>6.25</v>
+      </c>
+      <c r="BF200">
+        <v>2.07</v>
+      </c>
+      <c r="BG200">
+        <v>1.4</v>
+      </c>
+      <c r="BH200">
+        <v>2.65</v>
+      </c>
+      <c r="BI200">
+        <v>1.67</v>
+      </c>
+      <c r="BJ200">
+        <v>2.05</v>
+      </c>
+      <c r="BK200">
+        <v>2.08</v>
+      </c>
+      <c r="BL200">
+        <v>1.65</v>
+      </c>
+      <c r="BM200">
+        <v>2.7</v>
+      </c>
+      <c r="BN200">
+        <v>1.4</v>
+      </c>
+      <c r="BO200">
+        <v>3.65</v>
+      </c>
+      <c r="BP200">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="310">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,9 @@
     <t>['18', '33', '36', '57']</t>
   </si>
   <si>
+    <t>['20', '24', '26', '28']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1302,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,7 +1561,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1970,7 +1973,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2176,7 +2179,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2382,7 +2385,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2588,7 +2591,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2794,7 +2797,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3000,7 +3003,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3412,7 +3415,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3490,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ11">
         <v>1.8</v>
@@ -3824,7 +3827,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4111,7 +4114,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ14">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>1.83</v>
@@ -5678,7 +5681,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5756,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ22">
         <v>0.44</v>
@@ -6090,7 +6093,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6914,7 +6917,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8150,7 +8153,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8437,7 +8440,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8768,7 +8771,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8974,7 +8977,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9798,7 +9801,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10004,7 +10007,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10416,7 +10419,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10828,7 +10831,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11034,7 +11037,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12064,7 +12067,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12682,7 +12685,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13094,7 +13097,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13712,7 +13715,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13790,7 +13793,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ61">
         <v>2</v>
@@ -14124,7 +14127,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14205,7 +14208,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.68</v>
@@ -14536,7 +14539,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14742,7 +14745,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15360,7 +15363,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15566,7 +15569,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15978,7 +15981,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16059,7 +16062,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR72">
         <v>1.16</v>
@@ -16802,7 +16805,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17626,7 +17629,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17832,7 +17835,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17910,7 +17913,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18325,7 +18328,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ83">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR83">
         <v>1.07</v>
@@ -18862,7 +18865,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19274,7 +19277,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19480,7 +19483,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19892,7 +19895,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20098,7 +20101,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20510,7 +20513,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20922,7 +20925,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21618,7 +21621,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ99">
         <v>0.5600000000000001</v>
@@ -21952,7 +21955,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22158,7 +22161,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22364,7 +22367,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22982,7 +22985,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23806,7 +23809,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24299,7 +24302,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR112">
         <v>1.08</v>
@@ -24630,7 +24633,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25042,7 +25045,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25248,7 +25251,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25454,7 +25457,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25866,7 +25869,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26356,7 +26359,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122">
         <v>0.73</v>
@@ -26690,7 +26693,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27926,7 +27929,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28338,7 +28341,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28419,7 +28422,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ132">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28750,7 +28753,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28956,7 +28959,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29368,7 +29371,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29780,7 +29783,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29986,7 +29989,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30604,7 +30607,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30810,7 +30813,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30888,7 +30891,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ144">
         <v>1.2</v>
@@ -31222,7 +31225,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31840,7 +31843,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32046,7 +32049,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32333,7 +32336,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ151">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR151">
         <v>1.39</v>
@@ -32664,7 +32667,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33076,7 +33079,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33282,7 +33285,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33694,7 +33697,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33900,7 +33903,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35136,7 +35139,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35548,7 +35551,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35960,7 +35963,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36038,7 +36041,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ169">
         <v>0.9</v>
@@ -36372,7 +36375,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36656,7 +36659,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ172">
         <v>1.27</v>
@@ -37071,7 +37074,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ174">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.33</v>
@@ -37608,7 +37611,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37814,7 +37817,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38020,7 +38023,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38226,7 +38229,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38844,7 +38847,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39256,7 +39259,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40080,7 +40083,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40904,7 +40907,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41316,7 +41319,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41728,7 +41731,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41934,7 +41937,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42137,7 +42140,7 @@
         <v>2</v>
       </c>
       <c r="O199" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="P199" t="s">
         <v>141</v>
@@ -42503,6 +42506,212 @@
       </c>
       <c r="BP200">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7465188</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45677.70833333334</v>
+      </c>
+      <c r="F201">
+        <v>20</v>
+      </c>
+      <c r="G201" t="s">
+        <v>79</v>
+      </c>
+      <c r="H201" t="s">
+        <v>77</v>
+      </c>
+      <c r="I201">
+        <v>4</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>4</v>
+      </c>
+      <c r="L201">
+        <v>4</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>4</v>
+      </c>
+      <c r="O201" t="s">
+        <v>230</v>
+      </c>
+      <c r="P201" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q201">
+        <v>2.38</v>
+      </c>
+      <c r="R201">
+        <v>2.1</v>
+      </c>
+      <c r="S201">
+        <v>5.5</v>
+      </c>
+      <c r="T201">
+        <v>1.44</v>
+      </c>
+      <c r="U201">
+        <v>2.63</v>
+      </c>
+      <c r="V201">
+        <v>3.25</v>
+      </c>
+      <c r="W201">
+        <v>1.33</v>
+      </c>
+      <c r="X201">
+        <v>9</v>
+      </c>
+      <c r="Y201">
+        <v>1.07</v>
+      </c>
+      <c r="Z201">
+        <v>1.73</v>
+      </c>
+      <c r="AA201">
+        <v>3.5</v>
+      </c>
+      <c r="AB201">
+        <v>5.25</v>
+      </c>
+      <c r="AC201">
+        <v>1.06</v>
+      </c>
+      <c r="AD201">
+        <v>10</v>
+      </c>
+      <c r="AE201">
+        <v>1.35</v>
+      </c>
+      <c r="AF201">
+        <v>3.25</v>
+      </c>
+      <c r="AG201">
+        <v>2</v>
+      </c>
+      <c r="AH201">
+        <v>1.8</v>
+      </c>
+      <c r="AI201">
+        <v>1.95</v>
+      </c>
+      <c r="AJ201">
+        <v>1.8</v>
+      </c>
+      <c r="AK201">
+        <v>1.16</v>
+      </c>
+      <c r="AL201">
+        <v>1.27</v>
+      </c>
+      <c r="AM201">
+        <v>2.1</v>
+      </c>
+      <c r="AN201">
+        <v>1.44</v>
+      </c>
+      <c r="AO201">
+        <v>1.67</v>
+      </c>
+      <c r="AP201">
+        <v>1.6</v>
+      </c>
+      <c r="AQ201">
+        <v>1.5</v>
+      </c>
+      <c r="AR201">
+        <v>1.52</v>
+      </c>
+      <c r="AS201">
+        <v>1.19</v>
+      </c>
+      <c r="AT201">
+        <v>2.71</v>
+      </c>
+      <c r="AU201">
+        <v>8</v>
+      </c>
+      <c r="AV201">
+        <v>3</v>
+      </c>
+      <c r="AW201">
+        <v>7</v>
+      </c>
+      <c r="AX201">
+        <v>7</v>
+      </c>
+      <c r="AY201">
+        <v>16</v>
+      </c>
+      <c r="AZ201">
+        <v>10</v>
+      </c>
+      <c r="BA201">
+        <v>6</v>
+      </c>
+      <c r="BB201">
+        <v>5</v>
+      </c>
+      <c r="BC201">
+        <v>11</v>
+      </c>
+      <c r="BD201">
+        <v>1.47</v>
+      </c>
+      <c r="BE201">
+        <v>6.5</v>
+      </c>
+      <c r="BF201">
+        <v>3.05</v>
+      </c>
+      <c r="BG201">
+        <v>1.43</v>
+      </c>
+      <c r="BH201">
+        <v>2.55</v>
+      </c>
+      <c r="BI201">
+        <v>1.75</v>
+      </c>
+      <c r="BJ201">
+        <v>1.95</v>
+      </c>
+      <c r="BK201">
+        <v>2.18</v>
+      </c>
+      <c r="BL201">
+        <v>1.58</v>
+      </c>
+      <c r="BM201">
+        <v>2.85</v>
+      </c>
+      <c r="BN201">
+        <v>1.36</v>
+      </c>
+      <c r="BO201">
+        <v>3.8</v>
+      </c>
+      <c r="BP201">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="310">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1305,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5">
         <v>0.9</v>
@@ -7204,7 +7204,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ30">
         <v>1.9</v>
@@ -11115,7 +11115,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48">
         <v>1.8</v>
@@ -11530,7 +11530,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ50">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -14414,7 +14414,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ64">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -15647,7 +15647,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
         <v>0.9</v>
@@ -18534,7 +18534,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ84">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -18737,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ85">
         <v>0.44</v>
@@ -22857,7 +22857,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
         <v>1.2</v>
@@ -23890,7 +23890,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ110">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -26156,7 +26156,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ121">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -28419,7 +28419,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ132">
         <v>1.5</v>
@@ -31718,7 +31718,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ148">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -32539,7 +32539,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ152">
         <v>0.3</v>
@@ -34602,7 +34602,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ162">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -38513,7 +38513,7 @@
         <v>0.13</v>
       </c>
       <c r="AP181">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ181">
         <v>0.11</v>
@@ -40161,7 +40161,7 @@
         <v>0.25</v>
       </c>
       <c r="AP189">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ189">
         <v>0.5600000000000001</v>
@@ -40370,7 +40370,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ190">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -42712,6 +42712,212 @@
       </c>
       <c r="BP201">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7465195</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45681.70833333334</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>73</v>
+      </c>
+      <c r="H202" t="s">
+        <v>74</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>2</v>
+      </c>
+      <c r="O202" t="s">
+        <v>96</v>
+      </c>
+      <c r="P202" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q202">
+        <v>3.1</v>
+      </c>
+      <c r="R202">
+        <v>2.05</v>
+      </c>
+      <c r="S202">
+        <v>3.75</v>
+      </c>
+      <c r="T202">
+        <v>1.5</v>
+      </c>
+      <c r="U202">
+        <v>2.5</v>
+      </c>
+      <c r="V202">
+        <v>3.4</v>
+      </c>
+      <c r="W202">
+        <v>1.3</v>
+      </c>
+      <c r="X202">
+        <v>10</v>
+      </c>
+      <c r="Y202">
+        <v>1.06</v>
+      </c>
+      <c r="Z202">
+        <v>2.45</v>
+      </c>
+      <c r="AA202">
+        <v>3.1</v>
+      </c>
+      <c r="AB202">
+        <v>3</v>
+      </c>
+      <c r="AC202">
+        <v>1.08</v>
+      </c>
+      <c r="AD202">
+        <v>8.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.4</v>
+      </c>
+      <c r="AF202">
+        <v>3</v>
+      </c>
+      <c r="AG202">
+        <v>2.2</v>
+      </c>
+      <c r="AH202">
+        <v>1.67</v>
+      </c>
+      <c r="AI202">
+        <v>1.91</v>
+      </c>
+      <c r="AJ202">
+        <v>1.91</v>
+      </c>
+      <c r="AK202">
+        <v>1.36</v>
+      </c>
+      <c r="AL202">
+        <v>1.33</v>
+      </c>
+      <c r="AM202">
+        <v>1.57</v>
+      </c>
+      <c r="AN202">
+        <v>1.2</v>
+      </c>
+      <c r="AO202">
+        <v>0.78</v>
+      </c>
+      <c r="AP202">
+        <v>1.18</v>
+      </c>
+      <c r="AQ202">
+        <v>0.8</v>
+      </c>
+      <c r="AR202">
+        <v>1.36</v>
+      </c>
+      <c r="AS202">
+        <v>0.75</v>
+      </c>
+      <c r="AT202">
+        <v>2.11</v>
+      </c>
+      <c r="AU202">
+        <v>8</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>9</v>
+      </c>
+      <c r="AX202">
+        <v>12</v>
+      </c>
+      <c r="AY202">
+        <v>18</v>
+      </c>
+      <c r="AZ202">
+        <v>17</v>
+      </c>
+      <c r="BA202">
+        <v>4</v>
+      </c>
+      <c r="BB202">
+        <v>2</v>
+      </c>
+      <c r="BC202">
+        <v>6</v>
+      </c>
+      <c r="BD202">
+        <v>1.81</v>
+      </c>
+      <c r="BE202">
+        <v>6.4</v>
+      </c>
+      <c r="BF202">
+        <v>2.2</v>
+      </c>
+      <c r="BG202">
+        <v>1.34</v>
+      </c>
+      <c r="BH202">
+        <v>2.9</v>
+      </c>
+      <c r="BI202">
+        <v>1.58</v>
+      </c>
+      <c r="BJ202">
+        <v>2.18</v>
+      </c>
+      <c r="BK202">
+        <v>1.95</v>
+      </c>
+      <c r="BL202">
+        <v>1.74</v>
+      </c>
+      <c r="BM202">
+        <v>2.48</v>
+      </c>
+      <c r="BN202">
+        <v>1.47</v>
+      </c>
+      <c r="BO202">
+        <v>3.2</v>
+      </c>
+      <c r="BP202">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
